--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BE7FE3-B4A0-4D92-BA40-DFDE65D401EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08031104-B70D-4A7F-8047-6CECA935ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="112">
   <si>
     <t>Chart Type</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Sector</t>
   </si>
   <si>
-    <t>2021.0</t>
-  </si>
-  <si>
     <t>M1_C1_10</t>
   </si>
   <si>
@@ -321,13 +318,76 @@
   </si>
   <si>
     <t>2030, 2040, 2050</t>
+  </si>
+  <si>
+    <t>Renewable power, Energy efficiency, Other end use , Grids, Electric vehicle, Battery storage, Nuclear, Low-emission fuels and carbon capture utilisation and storage</t>
+  </si>
+  <si>
+    <t>East Asia and Pacific, North America (excl. Mexico), Europe, Eurasia, Latin America &amp; Caribbean, South Asia, Sub-Saharan Africa, Others</t>
+  </si>
+  <si>
+    <t>Fossil fuels, Renewable power, Power grids and storage, Nuclear and other clean power, Energy efficiency and end-use, Low-emissions fuels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other renewables (TWh, substituted energy), Biofuels (TWh, substituted energy), Solar (TWh, substituted energy), Coal (TWh, substituted energy), Gas (TWh, substituted energy), Oil (TWh, substituted energy), Wind (TWh, substituted energy), Nuclear (TWh, substituted energy), Hydropower (TWh, substituted energy), Traditional biomass (TWh, substituted energy)	</t>
+  </si>
+  <si>
+    <t>Copper, Lithium, Nickel, Manganese, Cobalt, Graphite, Zinc, Rare earths, Others</t>
+  </si>
+  <si>
+    <t>Oil, Electricity, Natural Gas, Coal</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>Sector and end use</t>
+  </si>
+  <si>
+    <t>Global greenhouse gas emission [%]</t>
+  </si>
+  <si>
+    <t>1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022</t>
+  </si>
+  <si>
+    <t>Coal [GtCO2 eq], Oil [GtCO2 eq], Natural gas [GtCO2 eq], Waste [GtCO2 eq], Industrial processes [GtCO2 eq], Methane [GtCO2 eq], Nitrous oxide [GtCO2 eq], CO2 flaring [GtCO2 eq]</t>
+  </si>
+  <si>
+    <t>Fuel / Power Generation Method</t>
+  </si>
+  <si>
+    <t>2021 (BCM), 2030 (BCM)</t>
+  </si>
+  <si>
+    <t>Country Income Level</t>
+  </si>
+  <si>
+    <t>Onshore wind (%), Solar PV (%)</t>
+  </si>
+  <si>
+    <t>LDVs, Bus, Other, Europe, China, United States, Other</t>
+  </si>
+  <si>
+    <t>Value Series Unit</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Tooltip</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>4Ws (%), 3Ws (%), 2Ws (%), Buses (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,6 +422,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -383,7 +469,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -440,20 +526,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -482,10 +559,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,8 +908,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED07C11-33D7-4B87-92FA-8D1ECFE94ACC}">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="34" style="5" customWidth="1"/>
     <col min="2" max="2" width="26.125" style="5" customWidth="1"/>
@@ -829,7 +917,7 @@
     <col min="5" max="5" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -840,7 +928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -851,7 +939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
         <v>6</v>
@@ -860,7 +948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -871,7 +959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
         <v>6</v>
@@ -883,7 +971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="78.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="78.75">
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
@@ -897,58 +985,52 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="1:5" ht="31.5">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="21"/>
+    </row>
+    <row r="9" spans="1:5" ht="31.5">
+      <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10" t="s">
+    <row r="10" spans="1:5" ht="31.5">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:5" s="20" customFormat="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="21"/>
+    </row>
+    <row r="12" spans="1:5" ht="31.5">
+      <c r="A12" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>4</v>
@@ -957,167 +1039,155 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:5" s="20" customFormat="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="21"/>
+    </row>
+    <row r="15" spans="1:5" ht="31.5">
+      <c r="A15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="20" customFormat="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="21"/>
+    </row>
+    <row r="18" spans="1:3" ht="31.5">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A16" s="8" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="21"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:3">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="31.5">
       <c r="A23" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="31.5">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="31.5">
+      <c r="A25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C27" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:3">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="21"/>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>27</v>
@@ -1126,14 +1196,88 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="20" customFormat="1" ht="31.5">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C34" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="21"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="20" customFormat="1">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>37</v>
       </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1142,15 +1286,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3995E8-5D59-A246-8C63-59455514011D}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1161,7 +1305,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1172,7 +1316,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1183,125 +1327,169 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
+      <c r="B10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C14" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="20" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A12" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C17" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="20" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
+      <c r="B18" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1313,15 +1501,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB9FE39-C79D-4DBC-8CB6-FC6DEC80E217}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
     <col min="2" max="2" width="21.1875" customWidth="1"/>
     <col min="3" max="3" width="119.8125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1332,137 +1520,203 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>57</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
-        <v>59</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1473,15 +1727,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CEC0AF-4E88-4F6D-877B-345E0A7F68A3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="37.875" customWidth="1"/>
     <col min="2" max="2" width="24.8125" customWidth="1"/>
     <col min="3" max="3" width="36.9375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1492,9 +1746,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -1503,47 +1757,80 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>12</v>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1553,13 +1840,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13371D-61B1-4787-B6C0-DFA9D5464E33}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="22.8125" customWidth="1"/>
+    <col min="3" max="3" width="69.1875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1570,116 +1858,229 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A5" t="s">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
+      <c r="B11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A8" t="s">
+      <c r="B12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>76</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A15" t="s">
-        <v>79</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1689,14 +2090,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F429-4C7B-4895-A1E5-BA108442352A}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1707,36 +2108,64 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+        <v>79</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1746,14 +2175,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BD176-9F92-427B-BA11-CAB9E4FAF49B}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="31.5625" customWidth="1"/>
     <col min="3" max="3" width="46.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1764,148 +2193,281 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C2" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C3" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C4" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A11" t="s">
-        <v>86</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+        <v>84</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+        <v>85</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+        <v>86</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1916,9 +2478,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E17E0D-A2D7-4821-BE01-41121B094069}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -1937,9 +2499,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673FA7AC-B98D-412E-950A-D07B543E46C1}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>

--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08031104-B70D-4A7F-8047-6CECA935ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91E3D1-56B0-4B1A-A9AD-8E231D709759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="8" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -371,9 +371,6 @@
     <t>Value Series Unit</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>Tooltip</t>
   </si>
   <si>
@@ -381,6 +378,9 @@
   </si>
   <si>
     <t>4Ws (%), 3Ws (%), 2Ws (%), Buses (%)</t>
+  </si>
+  <si>
+    <t>ADD UNIT</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -567,11 +567,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -986,8 +982,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="31.5">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="9" t="s">
@@ -995,11 +991,11 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="21"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="8" t="s">
@@ -1013,20 +1009,20 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="31.5">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="20" customFormat="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="21"/>
+    <row r="11" spans="1:5">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="8" t="s">
@@ -1040,20 +1036,20 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="20" customFormat="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="21"/>
+    <row r="14" spans="1:5">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" spans="1:5" ht="31.5">
       <c r="A15" s="8" t="s">
@@ -1067,20 +1063,20 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="20" customFormat="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="21"/>
+    <row r="17" spans="1:3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="19"/>
     </row>
     <row r="18" spans="1:3" ht="31.5">
       <c r="A18" s="8" t="s">
@@ -1094,8 +1090,8 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -1103,11 +1099,11 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="21"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
@@ -1170,8 +1166,8 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="9" t="s">
@@ -1179,11 +1175,11 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="21"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="19"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
@@ -1236,9 +1232,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="20" customFormat="1" ht="31.5">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18" t="s">
+    <row r="34" spans="1:3" ht="31.5">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C34" s="9" t="s">
@@ -1246,11 +1242,11 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="21"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="19"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
@@ -1263,9 +1259,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="20" customFormat="1">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C37" s="9" t="s">
@@ -1273,11 +1269,11 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="21"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1332,10 +1328,10 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
         <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1405,25 +1401,25 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1438,25 +1434,25 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1471,25 +1467,25 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1547,11 +1543,11 @@
       <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1580,11 +1576,11 @@
       <c r="A7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1613,11 +1609,11 @@
       <c r="A10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1646,11 +1642,11 @@
       <c r="A13" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1679,11 +1675,11 @@
       <c r="A16" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1712,11 +1708,11 @@
       <c r="A19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1772,11 +1768,11 @@
       <c r="A4" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1799,11 +1795,11 @@
       <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1826,11 +1822,11 @@
       <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1884,11 +1880,11 @@
       <c r="A4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1917,11 +1913,11 @@
       <c r="A7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1950,11 +1946,11 @@
       <c r="A10" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1983,11 +1979,11 @@
       <c r="A13" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2016,11 +2012,11 @@
       <c r="A16" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2049,11 +2045,11 @@
       <c r="A19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2076,11 +2072,11 @@
       <c r="A22" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2128,11 +2124,11 @@
       <c r="A4" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2161,11 +2157,11 @@
       <c r="A7" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2241,11 +2237,11 @@
       <c r="A6" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2274,11 +2270,11 @@
       <c r="A9" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2307,11 +2303,11 @@
       <c r="A12" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2340,11 +2336,11 @@
       <c r="A15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2367,11 +2363,11 @@
       <c r="A18" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2394,11 +2390,11 @@
       <c r="A21" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2409,7 +2405,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2419,22 +2415,22 @@
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2463,11 +2459,11 @@
       <c r="A27" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2518,26 +2514,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2778,10 +2754,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2798,20 +2805,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91E3D1-56B0-4B1A-A9AD-8E231D709759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="8" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -347,9 +347,6 @@
     <t>Global greenhouse gas emission [%]</t>
   </si>
   <si>
-    <t>1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022</t>
-  </si>
-  <si>
     <t>Coal [GtCO2 eq], Oil [GtCO2 eq], Natural gas [GtCO2 eq], Waste [GtCO2 eq], Industrial processes [GtCO2 eq], Methane [GtCO2 eq], Nitrous oxide [GtCO2 eq], CO2 flaring [GtCO2 eq]</t>
   </si>
   <si>
@@ -381,13 +378,16 @@
   </si>
   <si>
     <t>ADD UNIT</t>
+  </si>
+  <si>
+    <t>Energy (MtCO2e), Electricity/Heat (MtCO2e), Manufacturing/Construction (MtCO2e), Transportation (MtCO2e)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -429,13 +429,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -530,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -563,13 +556,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -991,11 +983,11 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="8" t="s">
@@ -1018,11 +1010,11 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="8" t="s">
@@ -1045,11 +1037,11 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="19"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" spans="1:5" ht="31.5">
       <c r="A15" s="8" t="s">
@@ -1072,11 +1064,11 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" spans="1:3" ht="31.5">
       <c r="A18" s="8" t="s">
@@ -1099,11 +1091,11 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="19"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
@@ -1175,11 +1167,11 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="19"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="18"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
@@ -1242,11 +1234,11 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="19"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="18"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
@@ -1269,11 +1261,11 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="19"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1328,10 +1320,10 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
         <v>108</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1415,11 +1407,11 @@
       <c r="A12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>107</v>
+      <c r="B12" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1448,11 +1440,11 @@
       <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>107</v>
+      <c r="B15" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1481,11 +1473,11 @@
       <c r="A18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>107</v>
+      <c r="B18" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1543,11 +1535,11 @@
       <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>107</v>
+      <c r="B4" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1576,11 +1568,11 @@
       <c r="A7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>107</v>
+      <c r="B7" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1609,11 +1601,11 @@
       <c r="A10" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>107</v>
+      <c r="B10" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1642,11 +1634,11 @@
       <c r="A13" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>107</v>
+      <c r="B13" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1675,11 +1667,11 @@
       <c r="A16" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>107</v>
+      <c r="B16" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1708,11 +1700,11 @@
       <c r="A19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>107</v>
+      <c r="B19" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1768,11 +1760,11 @@
       <c r="A4" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>107</v>
+      <c r="B4" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1795,11 +1787,11 @@
       <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>107</v>
+      <c r="B7" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1822,11 +1814,11 @@
       <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>107</v>
+      <c r="B10" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1880,11 +1872,11 @@
       <c r="A4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>107</v>
+      <c r="B4" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1913,11 +1905,11 @@
       <c r="A7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>107</v>
+      <c r="B7" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1946,11 +1938,11 @@
       <c r="A10" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>107</v>
+      <c r="B10" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1979,11 +1971,11 @@
       <c r="A13" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>107</v>
+      <c r="B13" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2012,11 +2004,11 @@
       <c r="A16" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>107</v>
+      <c r="B16" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2045,11 +2037,11 @@
       <c r="A19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>107</v>
+      <c r="B19" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2072,11 +2064,11 @@
       <c r="A22" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>107</v>
+      <c r="B22" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2124,11 +2116,11 @@
       <c r="A4" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>107</v>
+      <c r="B4" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2157,11 +2149,11 @@
       <c r="A7" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>107</v>
+      <c r="B7" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2218,8 +2210,8 @@
       <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>48</v>
+      <c r="C4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2230,18 +2222,18 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>107</v>
+      <c r="B6" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2262,19 +2254,19 @@
       <c r="B8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>101</v>
+      <c r="C8" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>107</v>
+      <c r="B9" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2285,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2296,18 +2288,18 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>107</v>
+      <c r="B12" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2318,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2329,18 +2321,18 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>107</v>
+      <c r="B15" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2363,11 +2355,11 @@
       <c r="A18" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>107</v>
+      <c r="B18" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2390,11 +2382,11 @@
       <c r="A21" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>107</v>
+      <c r="B21" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2405,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2415,22 +2407,22 @@
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
+      <c r="C23" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>107</v>
+      <c r="B24" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2452,18 +2444,18 @@
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>107</v>
+      <c r="B27" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2514,6 +2506,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2754,27 +2766,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2791,23 +2802,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37DF0FA1-9824-4010-947A-1E0D3D3462B8}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="3" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="164">
   <si>
     <t>Chart Type</t>
   </si>
@@ -89,6 +89,9 @@
     <t>Names of Dataset Columns representing different value series for each category</t>
   </si>
   <si>
+    <t>Value Series Unit</t>
+  </si>
+  <si>
     <t>Bar Chart Categories Horizontal</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>Name of the Dataset Column for Y values</t>
   </si>
   <si>
+    <t>Tooltip</t>
+  </si>
+  <si>
     <t>Scatter Chart</t>
   </si>
   <si>
@@ -176,6 +182,9 @@
     <t>Energy use per capita (GJ)</t>
   </si>
   <si>
+    <t>Country</t>
+  </si>
+  <si>
     <t>HDI</t>
   </si>
   <si>
@@ -200,87 +209,267 @@
     <t>World, OECD, Non-OECD</t>
   </si>
   <si>
+    <t>Quadrillion btu</t>
+  </si>
+  <si>
     <t>M1_C1_12</t>
   </si>
   <si>
     <t>2015, 2021</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>M1_C1_13</t>
   </si>
   <si>
-    <t>2015 (watts per capita), 2022 (watts per capita)</t>
+    <t>2015, 2022</t>
+  </si>
+  <si>
+    <t>Watts per capita</t>
+  </si>
+  <si>
+    <t>M1_C3_25_1</t>
+  </si>
+  <si>
+    <t>Electricity (USD/kWh)</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>M1_C3_25_2</t>
+  </si>
+  <si>
+    <t>Electricity (USD/kWh), Gasoline (USD/litre), Diesel (USD/litre)</t>
+  </si>
+  <si>
+    <t>Energy Prices</t>
+  </si>
+  <si>
+    <t>M2_C2_47_1</t>
+  </si>
+  <si>
+    <t>With access to electricity, Without access to electricity</t>
+  </si>
+  <si>
+    <t>Population (millions)</t>
+  </si>
+  <si>
+    <t>M2_C2_47_2</t>
+  </si>
+  <si>
+    <t>M2_C2_47_3</t>
+  </si>
+  <si>
+    <t>Urban, Rural</t>
+  </si>
+  <si>
+    <t>Share of population with access to electricity</t>
   </si>
   <si>
     <t>M2_C2_48</t>
   </si>
   <si>
+    <t>Annual increase in population with access, Annual increase in population</t>
+  </si>
+  <si>
+    <t>M2_C2_49</t>
+  </si>
+  <si>
+    <t>Annual increase in population with electricity access (Urban), Annual increase in population (Urban), Annual increase in population with electricity access (Rural), Annual increase in population (Rural)</t>
+  </si>
+  <si>
     <t>M2_C2_53</t>
   </si>
   <si>
+    <t>M2_C2_54_1</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Biomass, Charcoal, Coal, Electricity, Gas, Kerosene</t>
+  </si>
+  <si>
+    <t>Percentage of the population mainly using each fuel type</t>
+  </si>
+  <si>
+    <t>M2_C2_54_2</t>
+  </si>
+  <si>
+    <t>M2_C2_54_3</t>
+  </si>
+  <si>
     <t>M2_C2_55</t>
   </si>
   <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Cold deaths, Heat deaths</t>
+  </si>
+  <si>
     <t>M2_C2_56</t>
   </si>
   <si>
+    <t>Population needing cooling (from hot climates), Additional population needing cooling, AC penetration in 2000, AC penetration in 2022</t>
+  </si>
+  <si>
+    <t>M2_C2_58_1</t>
+  </si>
+  <si>
+    <t>Rural poor, Urban poor, Total at high risk</t>
+  </si>
+  <si>
+    <t>Population (thousand)</t>
+  </si>
+  <si>
+    <t>M2_C2_58_2</t>
+  </si>
+  <si>
+    <t>Proportion of total population at high risk, Share of women in total population at high risk</t>
+  </si>
+  <si>
     <t>M2_C2_59</t>
   </si>
   <si>
+    <t>Sub-Saharan Africa, Latin America and the Caribbean, Central Asia and Southern Asia, Western Asia and Northern Africa, Eastern Asia and South-eastern Asia, Oceania, Northern America and Europe, Unspecified countries</t>
+  </si>
+  <si>
+    <t>Commitments (USD billion)</t>
+  </si>
+  <si>
     <t>M2_C2_60</t>
   </si>
   <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Annual increase in population with access, Annual increase in population</t>
-  </si>
-  <si>
-    <t>Urban (%), Rural (%)</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Cold deaths (%), Heat deaths (%)</t>
-  </si>
-  <si>
-    <t>Population needing cooling (from hot climates) (%), Additional population needing cooling (%), AC penetration in 2000 (%), AC penetration in 2022 (%)</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa, Latin America and the Caribbean, Central Asia and Southern Asia, Western Asia and Northern Africa, Eastern Asia and South-eastern Asia, Oceania, Northern America and Europe, Unspecified countries</t>
-  </si>
-  <si>
     <t>LDCs (USD bn), LLDCs (USD bn), SIDS (USD bn)</t>
   </si>
   <si>
+    <t>M2_C2_61</t>
+  </si>
+  <si>
+    <t>Grid (USD bn), Mini-grid (USD bn), Stand-alone (USD bn), Total (USD bn)</t>
+  </si>
+  <si>
+    <t>USD billions</t>
+  </si>
+  <si>
+    <t>M2_C2_62_1</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>M2_C2_62_2</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>Share (%)</t>
+  </si>
+  <si>
+    <t>M2_C2_63_1</t>
+  </si>
+  <si>
+    <t>Sub-Saharan Africa, Rest of World</t>
+  </si>
+  <si>
+    <t>USD bn</t>
+  </si>
+  <si>
+    <t>M2_C2_63_2</t>
+  </si>
+  <si>
+    <t>Asset Type</t>
+  </si>
+  <si>
     <t>M3_C2_7</t>
   </si>
   <si>
-    <t>M3_C3_11</t>
-  </si>
-  <si>
-    <t>M3_C3_12</t>
+    <t>2030, 2040, 2050</t>
+  </si>
+  <si>
+    <t>thousand persons</t>
+  </si>
+  <si>
+    <t>M3_C3_11_1</t>
+  </si>
+  <si>
+    <t>Subsector</t>
+  </si>
+  <si>
+    <t>Graphite, Copper, Cobalt, Silicon, Nickel, Zinc, Manganese, Lithium, Others</t>
+  </si>
+  <si>
+    <t>Kilograms per vehicle</t>
+  </si>
+  <si>
+    <t>M3_C3_11_2</t>
+  </si>
+  <si>
+    <t>Kilograms per megawatt</t>
+  </si>
+  <si>
+    <t>M3_C3_12_1</t>
+  </si>
+  <si>
+    <t>Clean energy, Other uses</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>M3_C3_12_2</t>
+  </si>
+  <si>
+    <t>M3_C3_12_3</t>
+  </si>
+  <si>
+    <t>M3_C3_12_4</t>
   </si>
   <si>
     <t>M4_C1_1</t>
   </si>
   <si>
+    <t>Renewable power, Energy efficiency, Other end use , Grids, Electric vehicle, Battery storage, Nuclear, Low-emission fuels and carbon capture utilisation and storage</t>
+  </si>
+  <si>
+    <t>ADD UNIT</t>
+  </si>
+  <si>
     <t>M4_C1_3</t>
   </si>
   <si>
+    <t>East Asia and Pacific, North America (excl. Mexico), Europe, Eurasia, Latin America &amp; Caribbean, South Asia, Sub-Saharan Africa, Others</t>
+  </si>
+  <si>
     <t>M4_C1_4</t>
   </si>
   <si>
+    <t>Fossil fuels, Renewable power, Power grids and storage, Nuclear and other clean power, Energy efficiency and end-use, Low-emissions fuels</t>
+  </si>
+  <si>
     <t>M4_C1_8</t>
   </si>
   <si>
+    <t xml:space="preserve">Other renewables (TWh, substituted energy), Biofuels (TWh, substituted energy), Solar (TWh, substituted energy), Coal (TWh, substituted energy), Gas (TWh, substituted energy), Oil (TWh, substituted energy), Wind (TWh, substituted energy), Nuclear (TWh, substituted energy), Hydropower (TWh, substituted energy), Traditional biomass (TWh, substituted energy)	</t>
+  </si>
+  <si>
     <t>M4_C1_9</t>
   </si>
   <si>
+    <t>Copper, Lithium, Nickel, Manganese, Cobalt, Graphite, Zinc, Rare earths, Others</t>
+  </si>
+  <si>
     <t>M4_C2_16</t>
   </si>
   <si>
+    <t>Oil, Electricity, Natural Gas, Coal</t>
+  </si>
+  <si>
     <t>M4_C4_30</t>
   </si>
   <si>
@@ -290,21 +479,48 @@
     <t>M5_C2_13</t>
   </si>
   <si>
+    <t>Bar</t>
+  </si>
+  <si>
     <t>M6_C1_1</t>
   </si>
   <si>
+    <t>Sector and end use</t>
+  </si>
+  <si>
+    <t>Global greenhouse gas emission [%]</t>
+  </si>
+  <si>
     <t>M6_C1_2</t>
   </si>
   <si>
+    <t>Energy (MtCO2e), Electricity/Heat (MtCO2e), Manufacturing/Construction (MtCO2e), Transportation (MtCO2e)</t>
+  </si>
+  <si>
     <t>M6_C1_4</t>
   </si>
   <si>
+    <t>Coal [GtCO2 eq], Oil [GtCO2 eq], Natural gas [GtCO2 eq], Waste [GtCO2 eq], Industrial processes [GtCO2 eq], Methane [GtCO2 eq], Nitrous oxide [GtCO2 eq], CO2 flaring [GtCO2 eq]</t>
+  </si>
+  <si>
     <t>M6_C2_10</t>
   </si>
   <si>
+    <t>Fuel / Power Generation Method</t>
+  </si>
+  <si>
+    <t>2021 (BCM), 2030 (BCM)</t>
+  </si>
+  <si>
     <t>M6_C2_11</t>
   </si>
   <si>
+    <t>Country Income Level</t>
+  </si>
+  <si>
+    <t>Onshore wind (%), Solar PV (%)</t>
+  </si>
+  <si>
     <t>M6_C4_19</t>
   </si>
   <si>
@@ -314,80 +530,20 @@
     <t>M6_C4_21</t>
   </si>
   <si>
+    <t>4Ws (%), 3Ws (%), 2Ws (%), Buses (%)</t>
+  </si>
+  <si>
     <t>M6_C4_22</t>
   </si>
   <si>
-    <t>2030, 2040, 2050</t>
-  </si>
-  <si>
-    <t>Renewable power, Energy efficiency, Other end use , Grids, Electric vehicle, Battery storage, Nuclear, Low-emission fuels and carbon capture utilisation and storage</t>
-  </si>
-  <si>
-    <t>East Asia and Pacific, North America (excl. Mexico), Europe, Eurasia, Latin America &amp; Caribbean, South Asia, Sub-Saharan Africa, Others</t>
-  </si>
-  <si>
-    <t>Fossil fuels, Renewable power, Power grids and storage, Nuclear and other clean power, Energy efficiency and end-use, Low-emissions fuels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other renewables (TWh, substituted energy), Biofuels (TWh, substituted energy), Solar (TWh, substituted energy), Coal (TWh, substituted energy), Gas (TWh, substituted energy), Oil (TWh, substituted energy), Wind (TWh, substituted energy), Nuclear (TWh, substituted energy), Hydropower (TWh, substituted energy), Traditional biomass (TWh, substituted energy)	</t>
-  </si>
-  <si>
-    <t>Copper, Lithium, Nickel, Manganese, Cobalt, Graphite, Zinc, Rare earths, Others</t>
-  </si>
-  <si>
-    <t>Oil, Electricity, Natural Gas, Coal</t>
-  </si>
-  <si>
-    <t>Bar</t>
-  </si>
-  <si>
-    <t>Sector and end use</t>
-  </si>
-  <si>
-    <t>Global greenhouse gas emission [%]</t>
-  </si>
-  <si>
-    <t>Coal [GtCO2 eq], Oil [GtCO2 eq], Natural gas [GtCO2 eq], Waste [GtCO2 eq], Industrial processes [GtCO2 eq], Methane [GtCO2 eq], Nitrous oxide [GtCO2 eq], CO2 flaring [GtCO2 eq]</t>
-  </si>
-  <si>
-    <t>Fuel / Power Generation Method</t>
-  </si>
-  <si>
-    <t>2021 (BCM), 2030 (BCM)</t>
-  </si>
-  <si>
-    <t>Country Income Level</t>
-  </si>
-  <si>
-    <t>Onshore wind (%), Solar PV (%)</t>
-  </si>
-  <si>
     <t>LDVs, Bus, Other, Europe, China, United States, Other</t>
-  </si>
-  <si>
-    <t>Value Series Unit</t>
-  </si>
-  <si>
-    <t>Tooltip</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>4Ws (%), 3Ws (%), 2Ws (%), Buses (%)</t>
-  </si>
-  <si>
-    <t>ADD UNIT</t>
-  </si>
-  <si>
-    <t>Energy (MtCO2e), Electricity/Heat (MtCO2e), Manufacturing/Construction (MtCO2e), Transportation (MtCO2e)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -441,8 +597,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +623,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -519,11 +693,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -562,6 +751,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -916,7 +1117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="30.75">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -936,7 +1137,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="30.75">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -985,13 +1186,13 @@
     <row r="8" spans="1:5">
       <c r="A8" s="17"/>
       <c r="B8" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>4</v>
@@ -1012,13 +1213,13 @@
     <row r="11" spans="1:5">
       <c r="A11" s="17"/>
       <c r="B11" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>4</v>
@@ -1033,19 +1234,19 @@
         <v>12</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="17"/>
       <c r="B14" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C14" s="18"/>
     </row>
-    <row r="15" spans="1:5" ht="31.5">
+    <row r="15" spans="1:5" ht="30.75">
       <c r="A15" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>4</v>
@@ -1060,19 +1261,19 @@
         <v>12</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="17"/>
       <c r="B17" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C17" s="18"/>
     </row>
     <row r="18" spans="1:3" ht="31.5">
       <c r="A18" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>4</v>
@@ -1087,25 +1288,25 @@
         <v>12</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="17"/>
       <c r="B20" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C20" s="18"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1114,18 +1315,18 @@
         <v>6</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="31.5">
       <c r="A23" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="31.5">
@@ -1134,136 +1335,136 @@
         <v>6</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="31.5">
       <c r="A25" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="8"/>
       <c r="B26" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17"/>
       <c r="B28" s="17" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="C28" s="18"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="31.5">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C35" s="18"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="17"/>
       <c r="B38" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C38" s="18"/>
     </row>
@@ -1274,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3995E8-5D59-A246-8C63-59455514011D}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1284,95 +1485,95 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>40</v>
+      <c r="A2" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>40</v>
+      <c r="A3" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="21" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
+      <c r="A5" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>44</v>
+      <c r="A6" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>44</v>
+      <c r="A7" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>47</v>
+      <c r="A8" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>47</v>
+      <c r="A9" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -1382,41 +1583,41 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>49</v>
+      <c r="A10" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>49</v>
+      <c r="A11" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>49</v>
+      <c r="A12" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>51</v>
+      <c r="A13" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1426,30 +1627,30 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>51</v>
+      <c r="A14" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>51</v>
+      <c r="A15" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>53</v>
+      <c r="A16" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1459,25 +1660,80 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>53</v>
+      <c r="A17" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>53</v>
+      <c r="A18" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1489,222 +1745,651 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB9FE39-C79D-4DBC-8CB6-FC6DEC80E217}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
-    <col min="2" max="2" width="21.1875" customWidth="1"/>
-    <col min="3" max="3" width="119.8125" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
+    <col min="3" max="3" width="119.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>55</v>
+      <c r="A2" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>62</v>
+      <c r="A3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>55</v>
+      <c r="A4" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>110</v>
+    <row r="57" spans="1:3">
+      <c r="A57" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1715,110 +2400,254 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CEC0AF-4E88-4F6D-877B-345E0A7F68A3}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="37.875" customWidth="1"/>
-    <col min="2" max="2" width="24.8125" customWidth="1"/>
-    <col min="3" max="3" width="36.9375" customWidth="1"/>
+    <col min="2" max="2" width="24.875" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>110</v>
+        <v>14</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1831,90 +2660,90 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="22.8125" customWidth="1"/>
-    <col min="3" max="3" width="69.1875" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="69.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
@@ -1925,62 +2754,62 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -1991,62 +2820,62 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
@@ -2054,7 +2883,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>12</v>
@@ -2062,13 +2891,13 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2087,18 +2916,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -2106,7 +2935,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
@@ -2114,29 +2943,29 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
@@ -2147,13 +2976,13 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2166,178 +2995,178 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="31.5625" customWidth="1"/>
+    <col min="2" max="2" width="31.625" customWidth="1"/>
     <col min="3" max="3" width="46.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>4</v>
@@ -2345,7 +3174,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>12</v>
@@ -2353,62 +3182,62 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -2416,46 +3245,46 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2470,13 +3299,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2491,13 +3320,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2767,39 +3596,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37DF0FA1-9824-4010-947A-1E0D3D3462B8}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB965BE-1417-4BA9-9E00-098E8B056A94}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="3" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="6" activeTab="4" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="172">
   <si>
     <t>Chart Type</t>
   </si>
@@ -287,93 +287,93 @@
     <t>M2_C2_54_1</t>
   </si>
   <si>
+    <t>Biomass, Charcoal, Coal, Electricity, Gas, Kerosene</t>
+  </si>
+  <si>
+    <t>M2_C2_54_2</t>
+  </si>
+  <si>
+    <t>M2_C2_54_3</t>
+  </si>
+  <si>
+    <t>M2_C2_55</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Cold deaths, Heat deaths</t>
+  </si>
+  <si>
+    <t>M2_C2_56</t>
+  </si>
+  <si>
+    <t>Population needing cooling (from hot climates), Additional population needing cooling, AC penetration in 2000, AC penetration in 2022</t>
+  </si>
+  <si>
+    <t>M2_C2_58_1</t>
+  </si>
+  <si>
+    <t>Rural poor, Urban poor, Total at high risk</t>
+  </si>
+  <si>
+    <t>Population (thousand)</t>
+  </si>
+  <si>
+    <t>M2_C2_58_2</t>
+  </si>
+  <si>
+    <t>Proportion of total population at high risk, Share of women in total population at high risk</t>
+  </si>
+  <si>
+    <t>M2_C2_59</t>
+  </si>
+  <si>
+    <t>Sub-Saharan Africa, Latin America and the Caribbean, Central Asia and Southern Asia, Western Asia and Northern Africa, Eastern Asia and South-eastern Asia, Oceania, Northern America and Europe, Unspecified countries</t>
+  </si>
+  <si>
+    <t>Commitments (USD billion)</t>
+  </si>
+  <si>
+    <t>M2_C2_60</t>
+  </si>
+  <si>
+    <t>LDCs (USD bn), LLDCs (USD bn), SIDS (USD bn)</t>
+  </si>
+  <si>
+    <t>M2_C2_61</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Grid (USD bn), Mini-grid (USD bn), Stand-alone (USD bn), Total (USD bn)</t>
+  </si>
+  <si>
+    <t>USD billions</t>
+  </si>
+  <si>
+    <t>M2_C2_62_1</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>M2_C2_62_2</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>Share (%)</t>
+  </si>
+  <si>
+    <t>M2_C2_63_1</t>
+  </si>
+  <si>
     <t>Period</t>
   </si>
   <si>
-    <t>Biomass, Charcoal, Coal, Electricity, Gas, Kerosene</t>
-  </si>
-  <si>
-    <t>Percentage of the population mainly using each fuel type</t>
-  </si>
-  <si>
-    <t>M2_C2_54_2</t>
-  </si>
-  <si>
-    <t>M2_C2_54_3</t>
-  </si>
-  <si>
-    <t>M2_C2_55</t>
-  </si>
-  <si>
-    <t>Entity</t>
-  </si>
-  <si>
-    <t>Cold deaths, Heat deaths</t>
-  </si>
-  <si>
-    <t>M2_C2_56</t>
-  </si>
-  <si>
-    <t>Population needing cooling (from hot climates), Additional population needing cooling, AC penetration in 2000, AC penetration in 2022</t>
-  </si>
-  <si>
-    <t>M2_C2_58_1</t>
-  </si>
-  <si>
-    <t>Rural poor, Urban poor, Total at high risk</t>
-  </si>
-  <si>
-    <t>Population (thousand)</t>
-  </si>
-  <si>
-    <t>M2_C2_58_2</t>
-  </si>
-  <si>
-    <t>Proportion of total population at high risk, Share of women in total population at high risk</t>
-  </si>
-  <si>
-    <t>M2_C2_59</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa, Latin America and the Caribbean, Central Asia and Southern Asia, Western Asia and Northern Africa, Eastern Asia and South-eastern Asia, Oceania, Northern America and Europe, Unspecified countries</t>
-  </si>
-  <si>
-    <t>Commitments (USD billion)</t>
-  </si>
-  <si>
-    <t>M2_C2_60</t>
-  </si>
-  <si>
-    <t>LDCs (USD bn), LLDCs (USD bn), SIDS (USD bn)</t>
-  </si>
-  <si>
-    <t>M2_C2_61</t>
-  </si>
-  <si>
-    <t>Grid (USD bn), Mini-grid (USD bn), Stand-alone (USD bn), Total (USD bn)</t>
-  </si>
-  <si>
-    <t>USD billions</t>
-  </si>
-  <si>
-    <t>M2_C2_62_1</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <t>M2_C2_62_2</t>
-  </si>
-  <si>
-    <t>Solution</t>
-  </si>
-  <si>
-    <t>Share (%)</t>
-  </si>
-  <si>
-    <t>M2_C2_63_1</t>
-  </si>
-  <si>
     <t>Sub-Saharan Africa, Rest of World</t>
   </si>
   <si>
@@ -434,10 +434,10 @@
     <t>M4_C1_1</t>
   </si>
   <si>
-    <t>Renewable power, Energy efficiency, Other end use , Grids, Electric vehicle, Battery storage, Nuclear, Low-emission fuels and carbon capture utilisation and storage</t>
-  </si>
-  <si>
-    <t>ADD UNIT</t>
+    <t>Renewable power, Energy efficiency, Other end use, Grids, Electric vehicle, Battery storage, Nuclear, Low-emission fuels and carbon capture utilisation and storage</t>
+  </si>
+  <si>
+    <t>Billion USD</t>
   </si>
   <si>
     <t>M4_C1_3</t>
@@ -455,7 +455,10 @@
     <t>M4_C1_8</t>
   </si>
   <si>
-    <t xml:space="preserve">Other renewables (TWh, substituted energy), Biofuels (TWh, substituted energy), Solar (TWh, substituted energy), Coal (TWh, substituted energy), Gas (TWh, substituted energy), Oil (TWh, substituted energy), Wind (TWh, substituted energy), Nuclear (TWh, substituted energy), Hydropower (TWh, substituted energy), Traditional biomass (TWh, substituted energy)	</t>
+    <t>Other renewables, Biofuels, Solar, Coal, Gas, Oil, Wind, Nuclear, Hydropower, Traditional biomass</t>
+  </si>
+  <si>
+    <t>Twh</t>
   </si>
   <si>
     <t>M4_C1_9</t>
@@ -464,22 +467,22 @@
     <t>Copper, Lithium, Nickel, Manganese, Cobalt, Graphite, Zinc, Rare earths, Others</t>
   </si>
   <si>
+    <t>kg per vehicle</t>
+  </si>
+  <si>
     <t>M4_C2_16</t>
   </si>
   <si>
     <t>Oil, Electricity, Natural Gas, Coal</t>
   </si>
   <si>
-    <t>M4_C4_30</t>
-  </si>
-  <si>
-    <t>M5_C1_10</t>
-  </si>
-  <si>
-    <t>M5_C2_13</t>
-  </si>
-  <si>
-    <t>Bar</t>
+    <t>M4_C3_37_1</t>
+  </si>
+  <si>
+    <t>M4_C3_37_2</t>
+  </si>
+  <si>
+    <t>Renewables, Increased demand, Replacement</t>
   </si>
   <si>
     <t>M6_C1_1</t>
@@ -494,13 +497,19 @@
     <t>M6_C1_2</t>
   </si>
   <si>
-    <t>Energy (MtCO2e), Electricity/Heat (MtCO2e), Manufacturing/Construction (MtCO2e), Transportation (MtCO2e)</t>
+    <t>Energy, Electricity/Heat, Manufacturing/Construction, Transportation</t>
+  </si>
+  <si>
+    <t>MtCo2e</t>
   </si>
   <si>
     <t>M6_C1_4</t>
   </si>
   <si>
-    <t>Coal [GtCO2 eq], Oil [GtCO2 eq], Natural gas [GtCO2 eq], Waste [GtCO2 eq], Industrial processes [GtCO2 eq], Methane [GtCO2 eq], Nitrous oxide [GtCO2 eq], CO2 flaring [GtCO2 eq]</t>
+    <t>Coal, Oil, Natural gas, Waste, Industrial processes, Methane, Nitrous oxide, CO2 flaring</t>
+  </si>
+  <si>
+    <t>GtCO2 eq</t>
   </si>
   <si>
     <t>M6_C2_10</t>
@@ -509,7 +518,10 @@
     <t>Fuel / Power Generation Method</t>
   </si>
   <si>
-    <t>2021 (BCM), 2030 (BCM)</t>
+    <t>2021, 2030</t>
+  </si>
+  <si>
+    <t>BCM</t>
   </si>
   <si>
     <t>M6_C2_11</t>
@@ -518,32 +530,44 @@
     <t>Country Income Level</t>
   </si>
   <si>
-    <t>Onshore wind (%), Solar PV (%)</t>
+    <t>Onshore wind , Solar PV</t>
   </si>
   <si>
     <t>M6_C4_19</t>
   </si>
   <si>
-    <t>M6_C4_20</t>
+    <t>Residential, Non-residential, Buildings construction industry, Other construction industry, Other</t>
+  </si>
+  <si>
+    <t>EJ</t>
   </si>
   <si>
     <t>M6_C4_21</t>
   </si>
   <si>
-    <t>4Ws (%), 3Ws (%), 2Ws (%), Buses (%)</t>
-  </si>
-  <si>
-    <t>M6_C4_22</t>
-  </si>
-  <si>
-    <t>LDVs, Bus, Other, Europe, China, United States, Other</t>
+    <t>4Ws,  3Ws, 2Ws, Buses</t>
+  </si>
+  <si>
+    <t>M6_C4_22_1</t>
+  </si>
+  <si>
+    <t>LDVs, Bus, Other</t>
+  </si>
+  <si>
+    <t>GWh per year</t>
+  </si>
+  <si>
+    <t>M6_C4_22_2</t>
+  </si>
+  <si>
+    <t>Europe, China, United States, Other</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -585,11 +609,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <sz val="12"/>
@@ -712,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -745,18 +764,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1184,11 +1200,11 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="18"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="8" t="s">
@@ -1211,11 +1227,11 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="18"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="17"/>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="8" t="s">
@@ -1238,11 +1254,11 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="18"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" spans="1:5" ht="30.75">
       <c r="A15" s="8" t="s">
@@ -1265,11 +1281,11 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="18"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="1:3" ht="31.5">
       <c r="A18" s="8" t="s">
@@ -1292,11 +1308,11 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="18"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
@@ -1368,11 +1384,11 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17" t="s">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="18"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
@@ -1435,11 +1451,11 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="18"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="17"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
@@ -1462,11 +1478,11 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="18"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1495,7 +1511,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>42</v>
       </c>
       <c r="B2" t="s">
@@ -1506,7 +1522,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>42</v>
       </c>
       <c r="B3" t="s">
@@ -1517,7 +1533,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>42</v>
       </c>
       <c r="B4" t="s">
@@ -1528,7 +1544,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1539,7 +1555,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B6" t="s">
@@ -1550,7 +1566,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1561,7 +1577,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B8" t="s">
@@ -1572,7 +1588,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1583,7 +1599,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -1594,7 +1610,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
       <c r="B11" t="s">
@@ -1605,10 +1621,10 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1616,7 +1632,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>55</v>
       </c>
       <c r="B13" t="s">
@@ -1627,7 +1643,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>55</v>
       </c>
       <c r="B14" t="s">
@@ -1638,10 +1654,10 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1649,7 +1665,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B16" t="s">
@@ -1660,7 +1676,7 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B17" t="s">
@@ -1671,10 +1687,10 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1682,7 +1698,7 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B19" t="s">
@@ -1693,7 +1709,7 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1704,7 +1720,7 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -1715,7 +1731,7 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -1726,10 +1742,10 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
@@ -1765,7 +1781,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>67</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1776,7 +1792,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1788,10 +1804,10 @@
       <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1799,7 +1815,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1810,7 +1826,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>70</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1821,10 +1837,10 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1832,32 +1848,32 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1865,7 +1881,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>74</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1876,7 +1892,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>74</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -1887,10 +1903,10 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1898,18 +1914,18 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>76</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="20" t="s">
         <v>76</v>
       </c>
       <c r="B15" s="10" t="s">
@@ -1920,10 +1936,10 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1931,7 +1947,7 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -1942,7 +1958,7 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>78</v>
       </c>
       <c r="B18" s="10" t="s">
@@ -1953,10 +1969,10 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1964,131 +1980,131 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="21" t="s">
-        <v>83</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="21" t="s">
-        <v>83</v>
+      <c r="A24" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="20" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="18" t="s">
+      <c r="B25" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="20" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="21" t="s">
-        <v>84</v>
+      <c r="A27" s="20" t="s">
+        <v>82</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="21" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -2096,8 +2112,8 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="21" t="s">
-        <v>88</v>
+      <c r="A32" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>4</v>
@@ -2107,21 +2123,21 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="21" t="s">
-        <v>88</v>
+      <c r="A33" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="17" t="s">
+      <c r="A34" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -2129,8 +2145,8 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="21" t="s">
-        <v>90</v>
+      <c r="A35" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>4</v>
@@ -2140,30 +2156,30 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="9" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="20" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="21" t="s">
-        <v>93</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>4</v>
@@ -2173,30 +2189,30 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="21" t="s">
-        <v>95</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>4</v>
@@ -2206,30 +2222,30 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="20" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>28</v>
@@ -2239,64 +2255,64 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="21" t="s">
-        <v>98</v>
+      <c r="A45" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="22" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="21" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="21" t="s">
+      <c r="B48" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="3" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" s="20" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="21" t="s">
-        <v>103</v>
-      </c>
       <c r="B50" s="8" t="s">
         <v>4</v>
       </c>
@@ -2305,52 +2321,52 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="21" t="s">
-        <v>103</v>
+      <c r="A51" s="20" t="s">
+        <v>102</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="20" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="21" t="s">
+      <c r="B52" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="21" t="s">
-        <v>105</v>
+      <c r="A53" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="21" t="s">
+      <c r="B54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="21" t="s">
-        <v>108</v>
+      <c r="A55" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>12</v>
@@ -2360,10 +2376,10 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="B56" s="17" t="s">
+      <c r="A56" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C56" t="s">
@@ -2371,25 +2387,25 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="20" t="s">
         <v>111</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="22" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="20" t="s">
         <v>111</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2420,7 +2436,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="20" t="s">
         <v>113</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2431,7 +2447,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="20" t="s">
         <v>113</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2442,10 +2458,10 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2453,18 +2469,18 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="20" t="s">
         <v>116</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="20" t="s">
         <v>116</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -2475,10 +2491,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="A7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -2486,18 +2502,18 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="A8" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="A9" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -2508,18 +2524,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="A10" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="A11" s="20" t="s">
         <v>122</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -2530,7 +2546,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="A12" s="20" t="s">
         <v>122</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -2541,10 +2557,10 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="A13" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -2552,7 +2568,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="A14" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -2563,7 +2579,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="A15" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -2574,10 +2590,10 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="A16" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2585,7 +2601,7 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="A17" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -2596,7 +2612,7 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="A18" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -2607,10 +2623,10 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" t="s">
+      <c r="A19" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -2618,7 +2634,7 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="A20" s="20" t="s">
         <v>127</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -2629,7 +2645,7 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" t="s">
+      <c r="A21" s="20" t="s">
         <v>127</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -2640,10 +2656,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" t="s">
+      <c r="A22" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -2657,9 +2673,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13371D-61B1-4787-B6C0-DFA9D5464E33}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="22.875" customWidth="1"/>
     <col min="3" max="3" width="69.25" customWidth="1"/>
   </cols>
@@ -2676,7 +2693,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2687,7 +2704,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2698,10 +2715,10 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2709,7 +2726,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -2720,7 +2737,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -2731,29 +2748,29 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="A7" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="A8" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="A9" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -2764,10 +2781,10 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="A10" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -2775,7 +2792,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="A11" s="20" t="s">
         <v>135</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -2786,7 +2803,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="A12" s="20" t="s">
         <v>135</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -2797,19 +2814,19 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="A13" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>137</v>
+      <c r="A14" s="20" t="s">
+        <v>138</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -2819,30 +2836,30 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>137</v>
+      <c r="A15" s="20" t="s">
+        <v>138</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="20" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>139</v>
+      <c r="A17" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -2852,21 +2869,21 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>139</v>
+      <c r="A18" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -2874,30 +2891,58 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>141</v>
+      <c r="A20" s="20" t="s">
+        <v>143</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>141</v>
+      <c r="A21" s="20" t="s">
+        <v>143</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>130</v>
+      <c r="A22" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2907,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F429-4C7B-4895-A1E5-BA108442352A}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -2923,66 +2968,6 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2995,6 +2980,7 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
+    <col min="1" max="1" width="45.75" customWidth="1"/>
     <col min="2" max="2" width="31.625" customWidth="1"/>
     <col min="3" max="3" width="46.75" customWidth="1"/>
   </cols>
@@ -3012,29 +2998,29 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -3045,29 +3031,29 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>28</v>
@@ -3078,213 +3064,225 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>151</v>
+      <c r="C8" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>152</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B21" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C22" t="s">
-        <v>45</v>
+      <c r="C22" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="C23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>130</v>
+        <v>170</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3335,26 +3333,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -3595,14 +3573,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB965BE-1417-4BA9-9E00-098E8B056A94}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C224E6D0-102B-4CDE-BDA8-E45F421AE3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="6" activeTab="4" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="1" activeTab="4" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="174">
   <si>
     <t>Chart Type</t>
   </si>
@@ -233,12 +233,12 @@
     <t>M1_C3_25_1</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>Electricity (USD/kWh)</t>
   </si>
   <si>
-    <t>Region</t>
-  </si>
-  <si>
     <t>M1_C3_25_2</t>
   </si>
   <si>
@@ -386,6 +386,12 @@
     <t>Asset Type</t>
   </si>
   <si>
+    <t>M2_C3_46</t>
+  </si>
+  <si>
+    <t>National electrification rate, Rural electrification rate</t>
+  </si>
+  <si>
     <t>M3_C2_7</t>
   </si>
   <si>
@@ -473,9 +479,6 @@
     <t>M4_C2_16</t>
   </si>
   <si>
-    <t>Oil, Electricity, Natural Gas, Coal</t>
-  </si>
-  <si>
     <t>M4_C3_37_1</t>
   </si>
   <si>
@@ -561,13 +564,16 @@
   </si>
   <si>
     <t>Europe, China, United States, Other</t>
+  </si>
+  <si>
+    <t>Oil, Electricity, Gas, Coal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1114,7 +1120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED07C11-33D7-4B87-92FA-8D1ECFE94ACC}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="34" style="5" customWidth="1"/>
     <col min="2" max="2" width="26.125" style="5" customWidth="1"/>
@@ -1122,7 +1128,7 @@
     <col min="5" max="5" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1133,7 +1139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30.75">
+    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
         <v>6</v>
@@ -1153,7 +1159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30.75">
+    <row r="4" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1164,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
         <v>6</v>
@@ -1176,7 +1182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="78.75">
+    <row r="6" spans="1:5" ht="78.75" x14ac:dyDescent="0.5">
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
@@ -1190,7 +1196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.5">
+    <row r="7" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
@@ -1199,14 +1205,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -1217,7 +1223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="31.5">
+    <row r="10" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
         <v>12</v>
@@ -1226,14 +1232,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A11" s="16"/>
       <c r="B11" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="17"/>
     </row>
-    <row r="12" spans="1:5" ht="31.5">
+    <row r="12" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
@@ -1244,7 +1250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
@@ -1253,14 +1259,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14" s="16"/>
       <c r="B14" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="17"/>
     </row>
-    <row r="15" spans="1:5" ht="30.75">
+    <row r="15" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A16" s="8"/>
       <c r="B16" s="8" t="s">
         <v>12</v>
@@ -1280,14 +1286,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" s="16"/>
       <c r="B17" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="17"/>
     </row>
-    <row r="18" spans="1:3" ht="31.5">
+    <row r="18" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
@@ -1298,7 +1304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" s="8"/>
       <c r="B19" s="8" t="s">
         <v>12</v>
@@ -1307,14 +1313,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" s="16"/>
       <c r="B20" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="17"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
@@ -1325,7 +1331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
         <v>6</v>
@@ -1334,7 +1340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="31.5">
+    <row r="23" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1345,7 +1351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="31.5">
+    <row r="24" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>6</v>
@@ -1354,7 +1360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="31.5">
+    <row r="25" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
@@ -1365,7 +1371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A26" s="8"/>
       <c r="B26" s="8" t="s">
         <v>28</v>
@@ -1374,7 +1380,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
@@ -1383,14 +1389,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A28" s="16"/>
       <c r="B28" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="17"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A29" s="8" t="s">
         <v>33</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>30</v>
@@ -1410,7 +1416,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A31" s="8" t="s">
         <v>34</v>
       </c>
@@ -1421,7 +1427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>30</v>
@@ -1430,7 +1436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
@@ -1441,7 +1447,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="31.5">
+    <row r="34" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>36</v>
@@ -1450,14 +1456,14 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A35" s="16"/>
       <c r="B35" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="17"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A36" s="8" t="s">
         <v>38</v>
       </c>
@@ -1468,7 +1474,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>36</v>
@@ -1477,7 +1483,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A38" s="16"/>
       <c r="B38" s="16" t="s">
         <v>14</v>
@@ -1492,14 +1498,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3995E8-5D59-A246-8C63-59455514011D}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -1510,7 +1516,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="20" t="s">
         <v>42</v>
       </c>
@@ -1521,7 +1527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="20" t="s">
         <v>42</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="20" t="s">
         <v>42</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" s="21" t="s">
         <v>42</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" s="20" t="s">
         <v>47</v>
       </c>
@@ -1565,7 +1571,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" s="21" t="s">
         <v>47</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
@@ -1587,7 +1593,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" s="21" t="s">
         <v>50</v>
       </c>
@@ -1598,7 +1604,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" s="20" t="s">
         <v>52</v>
       </c>
@@ -1609,7 +1615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" s="20" t="s">
         <v>52</v>
       </c>
@@ -1631,7 +1637,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" s="20" t="s">
         <v>55</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A14" s="20" t="s">
         <v>55</v>
       </c>
@@ -1653,7 +1659,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" s="20" t="s">
         <v>55</v>
       </c>
@@ -1664,7 +1670,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" s="20" t="s">
         <v>58</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" s="20" t="s">
         <v>58</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" s="20" t="s">
         <v>58</v>
       </c>
@@ -1697,29 +1703,29 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" s="20" t="s">
         <v>64</v>
       </c>
@@ -1727,10 +1733,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" s="20" t="s">
         <v>64</v>
       </c>
@@ -1741,7 +1747,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A23" s="20" t="s">
         <v>64</v>
       </c>
@@ -1761,15 +1767,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB9FE39-C79D-4DBC-8CB6-FC6DEC80E217}">
-  <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="3" width="119.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" s="20" t="s">
         <v>67</v>
       </c>
@@ -1791,7 +1797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -1803,7 +1809,7 @@
       </c>
       <c r="D3" s="14"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4" s="20" t="s">
         <v>67</v>
       </c>
@@ -1814,7 +1820,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A5" s="20" t="s">
         <v>70</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A6" s="20" t="s">
         <v>70</v>
       </c>
@@ -1836,7 +1842,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A7" s="20" t="s">
         <v>70</v>
       </c>
@@ -1847,7 +1853,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A8" s="20" t="s">
         <v>71</v>
       </c>
@@ -1858,7 +1864,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A9" s="20" t="s">
         <v>71</v>
       </c>
@@ -1869,7 +1875,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A10" s="20" t="s">
         <v>71</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A11" s="20" t="s">
         <v>74</v>
       </c>
@@ -1888,10 +1894,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A12" s="20" t="s">
         <v>74</v>
       </c>
@@ -1902,7 +1908,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A13" s="20" t="s">
         <v>74</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A14" s="20" t="s">
         <v>76</v>
       </c>
@@ -1921,10 +1927,10 @@
         <v>4</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A15" s="20" t="s">
         <v>76</v>
       </c>
@@ -1935,7 +1941,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A16" s="20" t="s">
         <v>76</v>
       </c>
@@ -1946,7 +1952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" s="20" t="s">
         <v>78</v>
       </c>
@@ -1954,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" s="20" t="s">
         <v>78</v>
       </c>
@@ -1968,7 +1974,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" s="20" t="s">
         <v>78</v>
       </c>
@@ -1979,7 +1985,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" s="20" t="s">
         <v>79</v>
       </c>
@@ -1990,7 +1996,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" s="20" t="s">
         <v>79</v>
       </c>
@@ -2001,7 +2007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" s="20" t="s">
         <v>79</v>
       </c>
@@ -2012,7 +2018,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A23" s="20" t="s">
         <v>81</v>
       </c>
@@ -2023,7 +2029,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A24" s="20" t="s">
         <v>81</v>
       </c>
@@ -2034,7 +2040,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A25" s="20" t="s">
         <v>81</v>
       </c>
@@ -2045,7 +2051,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A26" s="20" t="s">
         <v>82</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A27" s="20" t="s">
         <v>82</v>
       </c>
@@ -2067,7 +2073,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A28" s="20" t="s">
         <v>82</v>
       </c>
@@ -2078,7 +2084,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A29" s="20" t="s">
         <v>83</v>
       </c>
@@ -2089,7 +2095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A30" s="20" t="s">
         <v>83</v>
       </c>
@@ -2100,7 +2106,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A31" s="20" t="s">
         <v>83</v>
       </c>
@@ -2111,7 +2117,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A32" s="20" t="s">
         <v>86</v>
       </c>
@@ -2119,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A33" s="20" t="s">
         <v>86</v>
       </c>
@@ -2133,7 +2139,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A34" s="20" t="s">
         <v>86</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A35" s="20" t="s">
         <v>88</v>
       </c>
@@ -2155,7 +2161,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A36" s="20" t="s">
         <v>88</v>
       </c>
@@ -2166,7 +2172,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A37" s="20" t="s">
         <v>88</v>
       </c>
@@ -2177,7 +2183,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A38" s="20" t="s">
         <v>91</v>
       </c>
@@ -2188,7 +2194,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A39" s="20" t="s">
         <v>91</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A40" s="20" t="s">
         <v>91</v>
       </c>
@@ -2210,7 +2216,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A41" s="20" t="s">
         <v>93</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A42" s="20" t="s">
         <v>93</v>
       </c>
@@ -2232,7 +2238,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A43" s="20" t="s">
         <v>93</v>
       </c>
@@ -2243,7 +2249,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A44" s="20" t="s">
         <v>96</v>
       </c>
@@ -2254,7 +2260,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A45" s="20" t="s">
         <v>96</v>
       </c>
@@ -2265,7 +2271,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A46" s="20" t="s">
         <v>96</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A47" s="20" t="s">
         <v>98</v>
       </c>
@@ -2287,7 +2293,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A48" s="20" t="s">
         <v>98</v>
       </c>
@@ -2298,7 +2304,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A49" s="20" t="s">
         <v>98</v>
       </c>
@@ -2309,7 +2315,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A50" s="20" t="s">
         <v>102</v>
       </c>
@@ -2320,7 +2326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A51" s="20" t="s">
         <v>102</v>
       </c>
@@ -2331,7 +2337,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A52" s="20" t="s">
         <v>104</v>
       </c>
@@ -2342,7 +2348,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A53" s="20" t="s">
         <v>104</v>
       </c>
@@ -2353,7 +2359,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A54" s="20" t="s">
         <v>107</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A55" s="20" t="s">
         <v>107</v>
       </c>
@@ -2375,7 +2381,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A56" s="20" t="s">
         <v>107</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A57" s="20" t="s">
         <v>111</v>
       </c>
@@ -2397,7 +2403,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A58" s="20" t="s">
         <v>111</v>
       </c>
@@ -2406,6 +2412,39 @@
       </c>
       <c r="C58" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A59" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A60" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A61" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2417,14 +2456,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CEC0AF-4E88-4F6D-877B-345E0A7F68A3}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="37.875" customWidth="1"/>
     <col min="2" max="2" width="24.875" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2435,9 +2474,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -2446,97 +2485,97 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A7" s="20" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="20" t="s">
-        <v>116</v>
-      </c>
       <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A8" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="20" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A9" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>4</v>
@@ -2545,31 +2584,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A14" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -2578,31 +2617,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" s="20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" s="20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -2611,31 +2650,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A19" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
@@ -2644,26 +2683,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" s="20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2674,14 +2713,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13371D-61B1-4787-B6C0-DFA9D5464E33}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="22.875" customWidth="1"/>
     <col min="3" max="3" width="69.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2692,9 +2731,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -2703,31 +2742,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
@@ -2736,20 +2775,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>14</v>
@@ -2758,9 +2797,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
@@ -2769,31 +2808,31 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>28</v>
@@ -2802,31 +2841,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A14" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -2835,31 +2874,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" s="20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" s="20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -2868,31 +2907,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" s="20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" s="20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
@@ -2901,20 +2940,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
@@ -2923,20 +2962,20 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A23" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A24" s="20" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20" t="s">
-        <v>144</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>14</v>
@@ -2953,13 +2992,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F429-4C7B-4895-A1E5-BA108442352A}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2978,14 +3017,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BD176-9F92-427B-BA11-CAB9E4FAF49B}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="45.75" customWidth="1"/>
     <col min="2" max="2" width="31.625" customWidth="1"/>
     <col min="3" max="3" width="46.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2996,31 +3035,31 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>146</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -3029,31 +3068,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>149</v>
-      </c>
       <c r="B6" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>28</v>
@@ -3062,86 +3101,86 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>152</v>
-      </c>
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>155</v>
-      </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>159</v>
-      </c>
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>14</v>
@@ -3150,9 +3189,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>4</v>
@@ -3161,31 +3200,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>162</v>
-      </c>
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>4</v>
@@ -3194,20 +3233,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>165</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>14</v>
@@ -3216,9 +3255,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
@@ -3227,34 +3266,34 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>4</v>
@@ -3263,26 +3302,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
         <v>170</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3293,9 +3332,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E17E0D-A2D7-4821-BE01-41121B094069}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3314,9 +3353,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673FA7AC-B98D-412E-950A-D07B543E46C1}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3574,15 +3613,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
@@ -3593,14 +3623,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29019"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C224E6D0-102B-4CDE-BDA8-E45F421AE3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{876AACDA-2F6F-44C5-878E-C729B61DA8AD}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="1" activeTab="4" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="7" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="220">
   <si>
     <t>Chart Type</t>
   </si>
@@ -248,6 +248,60 @@
     <t>Energy Prices</t>
   </si>
   <si>
+    <t>M1_C3_18</t>
+  </si>
+  <si>
+    <t>Electricity Access, Clean Cooking Access</t>
+  </si>
+  <si>
+    <t>M1_C3_20</t>
+  </si>
+  <si>
+    <t>2020, 2010</t>
+  </si>
+  <si>
+    <t>million USD</t>
+  </si>
+  <si>
+    <t>M1_C3_21</t>
+  </si>
+  <si>
+    <t>PV Installed Capacity, Wind energy installed capacity, CSP installed capacity</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>M1_C3_30</t>
+  </si>
+  <si>
+    <t>Coal, Oil, Natural gas, Nuclear, Hydro, Tide, Biofuels, Waste, Wind, Solar PV, Solar thermal, Geothermal, Other sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GWh</t>
+  </si>
+  <si>
+    <t>M1_C3_31</t>
+  </si>
+  <si>
+    <t>Invisible, Sustainable Development Scenario, Buildings efficiency, Equipment efficiency, Stated Policies Scenario</t>
+  </si>
+  <si>
+    <t>Twh</t>
+  </si>
+  <si>
+    <t>M1_C3_25</t>
+  </si>
+  <si>
+    <t>High-impact, Medium-impact, Low-impact</t>
+  </si>
+  <si>
+    <t>M1_C1_37</t>
+  </si>
+  <si>
+    <t>All renewable, Variable renewable, Hydropower, Wind, Solar PV, Other renewable</t>
+  </si>
+  <si>
     <t>M2_C2_47_1</t>
   </si>
   <si>
@@ -422,10 +476,10 @@
     <t>M3_C3_12_1</t>
   </si>
   <si>
-    <t>Clean energy, Other uses</t>
-  </si>
-  <si>
-    <t>kt</t>
+    <t>Total use, APS, NZE</t>
+  </si>
+  <si>
+    <t>Mt</t>
   </si>
   <si>
     <t>M3_C3_12_2</t>
@@ -437,6 +491,12 @@
     <t>M3_C3_12_4</t>
   </si>
   <si>
+    <t>M3_C3_12_5</t>
+  </si>
+  <si>
+    <t>M3_C3_12_6</t>
+  </si>
+  <si>
     <t>M4_C1_1</t>
   </si>
   <si>
@@ -464,9 +524,6 @@
     <t>Other renewables, Biofuels, Solar, Coal, Gas, Oil, Wind, Nuclear, Hydropower, Traditional biomass</t>
   </si>
   <si>
-    <t>Twh</t>
-  </si>
-  <si>
     <t>M4_C1_9</t>
   </si>
   <si>
@@ -479,6 +536,9 @@
     <t>M4_C2_16</t>
   </si>
   <si>
+    <t>Oil, Electricity, Gas, Coal</t>
+  </si>
+  <si>
     <t>M4_C3_37_1</t>
   </si>
   <si>
@@ -566,14 +626,92 @@
     <t>Europe, China, United States, Other</t>
   </si>
   <si>
-    <t>Oil, Electricity, Gas, Coal</t>
+    <t>M7_C2_5</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Share of women (%)</t>
+  </si>
+  <si>
+    <t>M7_C2_8</t>
+  </si>
+  <si>
+    <t>Available data, Unavailable data</t>
+  </si>
+  <si>
+    <t>M8_C1_1</t>
+  </si>
+  <si>
+    <t>Coal, Oil, Natural Gas, Nuclear, Renewables</t>
+  </si>
+  <si>
+    <t>M8_C1_10</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>2020, 2021, 2022</t>
+  </si>
+  <si>
+    <t>Number of cyberattacks</t>
+  </si>
+  <si>
+    <t>M8_C2_12_1</t>
+  </si>
+  <si>
+    <t>New wind Capacity, Projected new wind capacity based on current growth rates, Annual capacity gap to meet net zero by 2050 scenarios</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>M8_C2_12_2</t>
+  </si>
+  <si>
+    <t>Cumulative wind capacity to meet net zero by 2050 scenarios (GW)</t>
+  </si>
+  <si>
+    <t>M8_C2_13</t>
+  </si>
+  <si>
+    <t>Global Installed Capacity (GW)</t>
+  </si>
+  <si>
+    <t>M8_C2_14</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Energy Potential (TWh)</t>
+  </si>
+  <si>
+    <t>M8_C3_15</t>
+  </si>
+  <si>
+    <t>Technology Area</t>
+  </si>
+  <si>
+    <t>China, India, Australia, Rest of World, UK, Other Europe, Canada, US</t>
+  </si>
+  <si>
+    <t>M8_C1_6</t>
+  </si>
+  <si>
+    <t>Coal,Gas,Clean firm,Hydro,Wind onshore,Wind offshore,Solar,Other</t>
+  </si>
+  <si>
+    <t>thousand TWh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -628,8 +766,19 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,6 +806,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -785,6 +940,14 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED07C11-33D7-4B87-92FA-8D1ECFE94ACC}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="34" style="5" customWidth="1"/>
     <col min="2" max="2" width="26.125" style="5" customWidth="1"/>
@@ -1128,7 +1291,7 @@
     <col min="5" max="5" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1139,7 +1302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="30.75">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -1150,7 +1313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
         <v>6</v>
@@ -1159,7 +1322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="30.75">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1170,7 +1333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
         <v>6</v>
@@ -1182,7 +1345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="78.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="78.75">
       <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
@@ -1196,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="31.5">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
@@ -1205,14 +1368,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5">
       <c r="A8" s="16"/>
       <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -1223,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="31.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
         <v>12</v>
@@ -1232,14 +1395,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5">
       <c r="A11" s="16"/>
       <c r="B11" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="17"/>
     </row>
-    <row r="12" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
@@ -1250,7 +1413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
         <v>12</v>
@@ -1259,14 +1422,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5">
       <c r="A14" s="16"/>
       <c r="B14" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="17"/>
     </row>
-    <row r="15" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="30.75">
       <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
@@ -1277,7 +1440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:5">
       <c r="A16" s="8"/>
       <c r="B16" s="8" t="s">
         <v>12</v>
@@ -1286,14 +1449,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:3">
       <c r="A17" s="16"/>
       <c r="B17" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="17"/>
     </row>
-    <row r="18" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" ht="31.5">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
@@ -1304,7 +1467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3">
       <c r="A19" s="8"/>
       <c r="B19" s="8" t="s">
         <v>12</v>
@@ -1313,14 +1476,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:3">
       <c r="A20" s="16"/>
       <c r="B20" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="17"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
@@ -1331,7 +1494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:3">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
         <v>6</v>
@@ -1340,7 +1503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:3" ht="31.5">
       <c r="A23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1351,7 +1514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:3" ht="31.5">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>6</v>
@@ -1360,7 +1523,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:3" ht="31.5">
       <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1534,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:3">
       <c r="A26" s="8"/>
       <c r="B26" s="8" t="s">
         <v>28</v>
@@ -1380,7 +1543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:3">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
@@ -1389,14 +1552,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:3">
       <c r="A28" s="16"/>
       <c r="B28" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="17"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
         <v>33</v>
       </c>
@@ -1407,7 +1570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>30</v>
@@ -1416,7 +1579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
         <v>34</v>
       </c>
@@ -1427,7 +1590,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:3">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
         <v>30</v>
@@ -1436,7 +1599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
         <v>35</v>
       </c>
@@ -1447,7 +1610,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:3" ht="31.5">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>36</v>
@@ -1456,14 +1619,14 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:3">
       <c r="A35" s="16"/>
       <c r="B35" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="17"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:3">
       <c r="A36" s="8" t="s">
         <v>38</v>
       </c>
@@ -1474,7 +1637,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:3">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>36</v>
@@ -1483,7 +1646,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:3">
       <c r="A38" s="16"/>
       <c r="B38" s="16" t="s">
         <v>14</v>
@@ -1497,15 +1660,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3995E8-5D59-A246-8C63-59455514011D}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -1516,7 +1679,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
         <v>42</v>
       </c>
@@ -1527,7 +1690,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
         <v>42</v>
       </c>
@@ -1538,7 +1701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3">
       <c r="A4" s="20" t="s">
         <v>42</v>
       </c>
@@ -1549,7 +1712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3">
       <c r="A5" s="21" t="s">
         <v>42</v>
       </c>
@@ -1560,7 +1723,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3">
       <c r="A6" s="20" t="s">
         <v>47</v>
       </c>
@@ -1571,7 +1734,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3">
       <c r="A7" s="21" t="s">
         <v>47</v>
       </c>
@@ -1582,7 +1745,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3">
       <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
@@ -1593,7 +1756,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:3">
       <c r="A9" s="21" t="s">
         <v>50</v>
       </c>
@@ -1604,7 +1767,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
         <v>52</v>
       </c>
@@ -1615,7 +1778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
@@ -1626,7 +1789,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3">
       <c r="A12" s="20" t="s">
         <v>52</v>
       </c>
@@ -1637,7 +1800,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:3">
       <c r="A13" s="20" t="s">
         <v>55</v>
       </c>
@@ -1648,7 +1811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:3">
       <c r="A14" s="20" t="s">
         <v>55</v>
       </c>
@@ -1659,7 +1822,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3">
       <c r="A15" s="20" t="s">
         <v>55</v>
       </c>
@@ -1670,7 +1833,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:3">
       <c r="A16" s="20" t="s">
         <v>58</v>
       </c>
@@ -1681,7 +1844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:4">
       <c r="A17" s="20" t="s">
         <v>58</v>
       </c>
@@ -1692,7 +1855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:4">
       <c r="A18" s="20" t="s">
         <v>58</v>
       </c>
@@ -1703,7 +1866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:4">
       <c r="A19" s="20" t="s">
         <v>61</v>
       </c>
@@ -1714,7 +1877,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:4">
       <c r="A20" s="20" t="s">
         <v>61</v>
       </c>
@@ -1725,7 +1888,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:4">
       <c r="A21" s="20" t="s">
         <v>64</v>
       </c>
@@ -1736,7 +1899,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:4">
       <c r="A22" s="20" t="s">
         <v>64</v>
       </c>
@@ -1747,7 +1910,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:4">
       <c r="A23" s="20" t="s">
         <v>64</v>
       </c>
@@ -1756,6 +1919,238 @@
       </c>
       <c r="C23" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="25"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1768,14 +2163,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB9FE39-C79D-4DBC-8CB6-FC6DEC80E217}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="20.75" customWidth="1"/>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="3" width="119.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -1786,9 +2181,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:4">
       <c r="A2" s="20" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -1797,32 +2192,32 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4">
       <c r="A3" s="20" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D3" s="14"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4">
       <c r="A4" s="20" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
@@ -1831,31 +2226,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:4">
       <c r="A6" s="20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>28</v>
@@ -1864,31 +2259,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:4">
       <c r="A9" s="20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="20" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>4</v>
@@ -1897,31 +2292,31 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:4">
       <c r="A12" s="20" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="20" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="20" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -1930,31 +2325,31 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:4">
       <c r="A15" s="20" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="20" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -1963,20 +2358,20 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3">
       <c r="A18" s="20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>14</v>
@@ -1985,9 +2380,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:3">
       <c r="A20" s="20" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>28</v>
@@ -1996,20 +2391,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3">
       <c r="A21" s="20" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="20" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>14</v>
@@ -2018,9 +2413,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:3">
       <c r="A23" s="20" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>28</v>
@@ -2029,20 +2424,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:3">
       <c r="A24" s="20" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="20" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>14</v>
@@ -2051,9 +2446,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:3">
       <c r="A26" s="20" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>28</v>
@@ -2062,20 +2457,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:3">
       <c r="A27" s="20" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="20" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>14</v>
@@ -2084,31 +2479,31 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:3">
       <c r="A29" s="20" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="20" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="20" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>14</v>
@@ -2117,9 +2512,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:3">
       <c r="A32" s="20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>4</v>
@@ -2128,20 +2523,20 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:3">
       <c r="A33" s="20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>14</v>
@@ -2150,9 +2545,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:3">
       <c r="A35" s="20" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>4</v>
@@ -2161,31 +2556,31 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:3">
       <c r="A36" s="20" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="20" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="20" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>4</v>
@@ -2194,20 +2589,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:3">
       <c r="A39" s="20" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="20" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>14</v>
@@ -2216,9 +2611,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:3">
       <c r="A41" s="20" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>4</v>
@@ -2227,31 +2622,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:3">
       <c r="A42" s="20" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="20" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="20" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>28</v>
@@ -2260,64 +2655,64 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:3">
       <c r="A45" s="20" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="20" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="20" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.5">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="20" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="20" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="20" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>4</v>
@@ -2326,97 +2721,97 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:3">
       <c r="A51" s="20" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.5">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="20" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="20" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="20" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="20" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="20" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="20" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="20" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="20" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
@@ -2425,20 +2820,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:3">
       <c r="A60" s="20" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="20" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>14</v>
@@ -2455,15 +2850,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CEC0AF-4E88-4F6D-877B-345E0A7F68A3}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="37.875" customWidth="1"/>
     <col min="2" max="2" width="24.875" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2474,9 +2869,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -2485,97 +2880,97 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="20" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="20" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="20" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="20" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="20" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="20" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>4</v>
@@ -2584,31 +2979,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3">
       <c r="A12" s="20" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="20" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="20" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -2617,31 +3012,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3">
       <c r="A15" s="20" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="20" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="20" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -2650,31 +3045,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3">
       <c r="A18" s="20" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="20" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="20" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
@@ -2683,26 +3078,92 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3">
       <c r="A21" s="20" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="20" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2713,14 +3174,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13371D-61B1-4787-B6C0-DFA9D5464E33}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="22.875" customWidth="1"/>
     <col min="3" max="3" width="69.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -2731,9 +3192,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
@@ -2742,31 +3203,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="20" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="20" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
@@ -2775,20 +3236,20 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3">
       <c r="A6" s="20" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="20" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>14</v>
@@ -2797,9 +3258,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3">
       <c r="A8" s="20" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4</v>
@@ -2808,31 +3269,31 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:3">
       <c r="A9" s="20" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>28</v>
@@ -2841,31 +3302,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3">
       <c r="A12" s="20" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="20" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="20" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>4</v>
@@ -2874,31 +3335,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3">
       <c r="A15" s="20" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="20" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="20" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>4</v>
@@ -2907,31 +3368,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3">
       <c r="A18" s="20" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="20" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="20" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>4</v>
@@ -2940,42 +3401,42 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3">
       <c r="A21" s="20" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="20" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="20" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="20" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>14</v>
@@ -2992,13 +3453,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC40F429-4C7B-4895-A1E5-BA108442352A}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3017,14 +3478,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9BD176-9F92-427B-BA11-CAB9E4FAF49B}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="45.75" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="2" width="31.625" customWidth="1"/>
     <col min="3" max="3" width="46.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3035,31 +3496,31 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -3068,31 +3529,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>28</v>
@@ -3101,86 +3562,86 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>14</v>
@@ -3189,9 +3650,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>4</v>
@@ -3200,31 +3661,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>4</v>
@@ -3233,20 +3694,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>14</v>
@@ -3255,9 +3716,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>4</v>
@@ -3266,34 +3727,34 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>4</v>
@@ -3302,26 +3763,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3331,10 +3792,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E17E0D-A2D7-4821-BE01-41121B094069}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="16.25" customWidth="1"/>
+    <col min="2" max="2" width="17.75" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3343,6 +3809,61 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3352,10 +3873,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673FA7AC-B98D-412E-950A-D07B543E46C1}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -3364,6 +3890,237 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.5" customHeight="1">
+      <c r="A3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="46.5">
+      <c r="A12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3372,6 +4129,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -3612,60 +4389,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3863359-C84C-48AE-8A16-E4683147332C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
 </file>
--- a/02_Inputs/Metadata/Charts Config.xlsx
+++ b/02_Inputs/Metadata/Charts Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fschi\undp\dsc-energy-academy-data\02_Inputs\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{876AACDA-2F6F-44C5-878E-C729B61DA8AD}"/>
+  <xr:revisionPtr revIDLastSave="498" documentId="13_ncr:1_{7CC245DA-34C9-48DA-8BBA-878AAEC6E624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A0871DD-7580-4948-8C81-A56EA91C0364}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" firstSheet="7" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
+    <workbookView xWindow="28690" yWindow="-2640" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{5D435C48-ED6F-954F-BEFC-1FEE717E716D}"/>
   </bookViews>
   <sheets>
     <sheet name="Charts Templates" sheetId="2" r:id="rId1"/>
@@ -392,7 +392,7 @@
     <t>M2_C2_60</t>
   </si>
   <si>
-    <t>LDCs (USD bn), LLDCs (USD bn), SIDS (USD bn)</t>
+    <t>LDCs, LLDCs, SIDS</t>
   </si>
   <si>
     <t>M2_C2_61</t>
@@ -401,7 +401,7 @@
     <t>Scenario</t>
   </si>
   <si>
-    <t>Grid (USD bn), Mini-grid (USD bn), Stand-alone (USD bn), Total (USD bn)</t>
+    <t>Grid, Mini-grid, Stand-alone, Total</t>
   </si>
   <si>
     <t>USD billions</t>
@@ -410,7 +410,7 @@
     <t>M2_C2_62_1</t>
   </si>
   <si>
-    <t>Population</t>
+    <t>Population (billions)</t>
   </si>
   <si>
     <t>M2_C2_62_2</t>
@@ -4129,26 +4129,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -4389,8 +4369,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4398,5 +4398,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E10C63-E07D-4283-A96B-D06A7085F4F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A2D89-2C08-452A-A018-3C955AED2DFC}"/>
 </file>